--- a/Result/profitability/4966.xlsx
+++ b/Result/profitability/4966.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AM67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.58</v>
       </c>
       <c r="M2" t="n">
-        <v>7.78</v>
+        <v>7.54125</v>
       </c>
       <c r="N2" t="n">
-        <v>41.91625000000001</v>
+        <v>41.625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>7.05</v>
       </c>
       <c r="M3" t="n">
-        <v>7.465</v>
+        <v>7.34125</v>
       </c>
       <c r="N3" t="n">
-        <v>41.99125</v>
+        <v>41.7425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>10.02</v>
       </c>
       <c r="M4" t="n">
-        <v>7.63625</v>
+        <v>7.54625</v>
       </c>
       <c r="N4" t="n">
-        <v>42.13875</v>
+        <v>41.84375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>5.85</v>
       </c>
       <c r="M5" t="n">
-        <v>7.319999999999999</v>
+        <v>7.15875</v>
       </c>
       <c r="N5" t="n">
-        <v>42.1825</v>
+        <v>41.81874999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -8812,6 +8812,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>4249</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2541</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1708</v>
+      </c>
+      <c r="F67" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>596</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>14.02%</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>50</v>
+      </c>
+      <c r="J67" t="n">
+        <v>646</v>
+      </c>
+      <c r="K67" t="n">
+        <v>593</v>
+      </c>
+      <c r="L67" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="M67" t="n">
+        <v>8.414999999999999</v>
+      </c>
+      <c r="N67" t="n">
+        <v>41.9275</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.8900000000000006</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.1314623338257017</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>-0.09999999999999432</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>-0.002481389578163684</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>-1.289999999999999</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>-0.1441340782122904</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>-2.909999999999997</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>-0.06750173973556006</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
